--- a/lessons/wall/excels/student_similarity.xlsx
+++ b/lessons/wall/excels/student_similarity.xlsx
@@ -218,70 +218,64 @@
       <text>
         <t>2px, 
 -- 4 ONLY --
- ", / (x11), &lt; (x22), &gt; (x23), div (x22)</t>
+ ", &gt;</t>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>", / (x11), &lt; (x14), &gt; (x14), div (x9), 
+        <t>", &gt;, 
 -- 4 ONLY --
- 2px, &lt; (x8), &gt; (x9), div (x13)</t>
+ 2px</t>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>/ (x2), &lt;, &gt;, 
+        <t>&gt;, 
 -- 4 ONLY --
- ", / (x9), 2px, &lt; (x21), &gt; (x22), div (x22)</t>
+ ", 2px</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>/, &lt;, &gt; (x2), 
+        <t>&gt;, 
 -- 4 ONLY --
- ", / (x10), 2px, &lt; (x21), &gt; (x21), div (x22)</t>
+ ", 2px</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>/ (x11), &lt; (x16), &gt; (x16), div (x16), 
+        <t>&gt;, 
 -- 4 ONLY --
- ", 2px, &lt; (x6), &gt; (x7), div (x6)</t>
+ ", 2px</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>2px, &lt;, 
+        <t>2px, 
 -- 4 ONLY --
- ", / (x11), &lt; (x21), &gt; (x23), div (x22)</t>
+ ", &gt;</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>", 2px, &lt;, &gt;, div (x2), 
--- 4 ONLY --
- / (x11), &lt; (x21), &gt; (x22), div (x20)</t>
+        <t>", 2px, &gt;</t>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>", /, 2px, &lt; (x2), &gt; (x2), div (x2), 
--- 4 ONLY --
- / (x10), &lt; (x20), &gt; (x21), div (x20)</t>
+        <t>", 2px, &gt;</t>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
         <t>", 
 -- 4 ONLY --
- / (x11), 2px, &lt; (x22), &gt; (x23), div (x22)</t>
+ 2px, &gt;</t>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>", / (x4), 2px, &lt; (x8), &gt; (x8), div (x8), 
--- 4 ONLY --
- / (x7), &lt; (x14), &gt; (x15), div (x14)</t>
+        <t>", 2px, &gt;</t>
       </text>
     </comment>
     <comment ref="D5" authorId="0" shapeId="0">
@@ -363,9 +357,9 @@
     </comment>
     <comment ref="D6" authorId="0" shapeId="0">
       <text>
-        <t>", / (x11), &lt; (x14), &gt; (x14), div (x9), 
+        <t>", &gt;, 
 -- 20 ONLY --
- ! (x2), " (x11), - (x3), . (x3), /, 50px (x2), : (x4), ; (x3), = (x6), Board, Chess, Visit, W3Schools, a (x2), background, black, body (x2), cell (x4), class (x4), color, com (x2), dark (x4), doctype, height, href, https, style, w3schools, width, www</t>
+ ! (x2), " (x11), - (x3), . (x3), / (x12), 50px (x2), : (x4), ; (x3), &lt; (x14), = (x6), &gt; (x13), Board, Chess, Visit, W3Schools, a (x2), background, black, body (x2), cell (x4), class (x4), color, com (x2), dark (x4), div (x9), doctype, height, href, https, style, w3schools, width, www</t>
       </text>
     </comment>
     <comment ref="E6" authorId="0" shapeId="0">
@@ -498,140 +492,140 @@
       <text>
         <t>., 
 -- 30 ONLY --
-  , * (x2), ,, / (x2), &lt;, &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+ * (x2), ,, / (x2), 50, &lt;, &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
       </text>
     </comment>
     <comment ref="D9" authorId="0" shapeId="0">
+      <text>
+        <t>&gt;, 
+-- 30 ONLY --
+ * (x2), ,, ., / (x2), 50, &lt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <t>., / (x2), &lt;, &gt;, a (x2), black, 
+-- 30 ONLY --
+ * (x2), ,, 50, I (x2), able (x2), about, allignmenot, along, and, basic, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="0" shapeId="0">
+      <text>
+        <t>chess, 
+-- 30 ONLY --
+ * (x2), ,, ., / (x2), 50, &lt;, &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="K9" authorId="0" shapeId="0">
+      <text>
+        <t>/, &lt;, &gt;, html, 
+-- 30 ONLY --
+ * (x2), ,, ., /, 50, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="N9" authorId="0" shapeId="0">
       <text>
         <t>/ (x2), &lt;, &gt;, 
 -- 30 ONLY --
-  , * (x2), ,, ., I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="F9" authorId="0" shapeId="0">
-      <text>
-        <t>., / (x2), &lt;, &gt;, a (x2), black, 
+ * (x2), ,, ., 50, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="O9" authorId="0" shapeId="0">
+      <text>
+        <t>., &lt;, black, 
 -- 30 ONLY --
-  , * (x2), ,, I (x2), able (x2), about, allignmenot, along, and, basic, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="H9" authorId="0" shapeId="0">
+ * (x2), ,, / (x2), 50, &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="Q9" authorId="0" shapeId="0">
+      <text>
+        <t>&lt;, &gt;, black, 
+-- 30 ONLY --
+ * (x2), ,, ., / (x2), 50, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="R9" authorId="0" shapeId="0">
       <text>
         <t>chess, 
 -- 30 ONLY --
-  , * (x2), ,, ., / (x2), &lt;, &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="K9" authorId="0" shapeId="0">
-      <text>
-        <t>/, &lt;, &gt;, html, 
+ * (x2), ,, ., / (x2), 50, &lt;, &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="S9" authorId="0" shapeId="0">
+      <text>
+        <t>/, &lt;, &gt;, black, chess, 
 -- 30 ONLY --
-  , * (x2), ,, ., /, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="N9" authorId="0" shapeId="0">
+ * (x2), ,, ., /, 50, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, bus, but, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="W9" authorId="0" shapeId="0">
       <text>
         <t>/ (x2), &lt;, &gt;, 
 -- 30 ONLY --
-  , * (x2), ,, ., I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="O9" authorId="0" shapeId="0">
-      <text>
-        <t>., &lt;, black, 
--- 30 ONLY --
-  , * (x2), ,, / (x2), &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="Q9" authorId="0" shapeId="0">
-      <text>
-        <t>&lt;, &gt;, black, 
--- 30 ONLY --
-  , * (x2), ,, ., / (x2), I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="R9" authorId="0" shapeId="0">
-      <text>
-        <t>chess, 
--- 30 ONLY --
-  , * (x2), ,, ., / (x2), &lt;, &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="S9" authorId="0" shapeId="0">
-      <text>
-        <t>/, &lt;, &gt;, black, chess, 
--- 30 ONLY --
-  , * (x2), ,, ., /, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, bus, but, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="W9" authorId="0" shapeId="0">
-      <text>
-        <t>/ (x2), &lt;, &gt;, 
--- 30 ONLY --
-  , * (x2), ,, ., I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+ * (x2), ,, ., 50, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
       </text>
     </comment>
     <comment ref="D11" authorId="0" shapeId="0">
+      <text>
+        <t>&gt;, 
+-- 40 ONLY --
+ /, &lt;, &gt;, html</t>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="0" shapeId="0">
       <text>
         <t>/, &lt;, &gt; (x2), 
 -- 40 ONLY --
  html</t>
       </text>
     </comment>
-    <comment ref="F11" authorId="0" shapeId="0">
+    <comment ref="I11" authorId="0" shapeId="0">
+      <text>
+        <t>/, &lt;, &gt;, html, 
+-- 40 ONLY --
+ &gt;</t>
+      </text>
+    </comment>
+    <comment ref="N11" authorId="0" shapeId="0">
       <text>
         <t>/, &lt;, &gt; (x2), 
 -- 40 ONLY --
  html</t>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0">
-      <text>
-        <t>/, &lt;, &gt;, html, 
+    <comment ref="O11" authorId="0" shapeId="0">
+      <text>
+        <t>&lt;, 
 -- 40 ONLY --
- &gt;</t>
-      </text>
-    </comment>
-    <comment ref="N11" authorId="0" shapeId="0">
+ /, &gt; (x2), html</t>
+      </text>
+    </comment>
+    <comment ref="Q11" authorId="0" shapeId="0">
+      <text>
+        <t>&lt;, &gt;, 
+-- 40 ONLY --
+ /, &gt;, html</t>
+      </text>
+    </comment>
+    <comment ref="S11" authorId="0" shapeId="0">
       <text>
         <t>/, &lt;, &gt; (x2), 
 -- 40 ONLY --
  html</t>
       </text>
     </comment>
-    <comment ref="O11" authorId="0" shapeId="0">
-      <text>
-        <t>&lt;, 
--- 40 ONLY --
- /, &gt; (x2), html</t>
-      </text>
-    </comment>
-    <comment ref="Q11" authorId="0" shapeId="0">
-      <text>
-        <t>&lt;, &gt;, 
--- 40 ONLY --
- /, &gt;, html</t>
-      </text>
-    </comment>
-    <comment ref="S11" authorId="0" shapeId="0">
+    <comment ref="W11" authorId="0" shapeId="0">
       <text>
         <t>/, &lt;, &gt; (x2), 
 -- 40 ONLY --
  html</t>
       </text>
     </comment>
-    <comment ref="W11" authorId="0" shapeId="0">
-      <text>
-        <t>/, &lt;, &gt; (x2), 
--- 40 ONLY --
- html</t>
-      </text>
-    </comment>
     <comment ref="D14" authorId="0" shapeId="0">
       <text>
-        <t>/ (x11), &lt; (x16), &gt; (x16), div (x16), 
+        <t>&gt;, 
 -- 55 ONLY --
- /, 0px (x2), 440px, : (x2), ; (x2), green, margin, padding</t>
+ / (x12), 0px (x2), 440px, : (x2), ; (x2), &lt; (x16), &gt; (x15), div (x16), green, margin, padding</t>
       </text>
     </comment>
     <comment ref="E14" authorId="0" shapeId="0">
@@ -713,9 +707,9 @@
     </comment>
     <comment ref="D15" authorId="0" shapeId="0">
       <text>
-        <t>2px, &lt;, 
+        <t>2px, 
 -- 67 ONLY --
- -, ., 400px, : (x3), ; (x3), black, border (x2), class, collapse (x2), height, solid, table</t>
+ -, ., 400px, : (x3), ; (x3), &lt;, black, border (x2), class, collapse (x2), height, solid, table</t>
       </text>
     </comment>
     <comment ref="E15" authorId="0" shapeId="0">
@@ -830,9 +824,9 @@
     </comment>
     <comment ref="D17" authorId="0" shapeId="0">
       <text>
-        <t>", 2px, &lt;, &gt;, div (x2), 
+        <t>", 2px, &gt;, 
 -- 72 ONLY --
- !, (, ), - (x4), 10px (x2), 2px, 50px (x2), 5px (x2), : (x9), ; (x9), =, Inline, Not, background, black (x2), block, border, color, display, gray, height, inline, margin (x2), padding (x2), recommended, solid, style (x2), width, with</t>
+ !, (, ), - (x4), 10px (x2), 2px, 50px (x2), 5px (x2), : (x9), ; (x9), &lt;, =, Inline, Not, background, black (x2), block, border, color, display, div (x2), gray, height, inline, margin (x2), padding (x2), recommended, solid, style (x2), width, with</t>
       </text>
     </comment>
     <comment ref="E17" authorId="0" shapeId="0">
@@ -1005,9 +999,9 @@
     </comment>
     <comment ref="D19" authorId="0" shapeId="0">
       <text>
-        <t>", /, 2px, &lt; (x2), &gt; (x2), div (x2), 
+        <t>", 2px, &gt;, 
 -- 77 ONLY --
- ", -, 50px (x2), : (x3), ; (x3), =, background, black, board, chess, color, height, style, visit, w3schools, width</t>
+ ", -, /, 50px (x2), : (x3), ; (x3), &lt; (x2), =, &gt;, background, black, board, chess, color, div (x2), height, style, visit, w3schools, width</t>
       </text>
     </comment>
     <comment ref="E19" authorId="0" shapeId="0">
@@ -1192,9 +1186,9 @@
     </comment>
     <comment ref="D23" authorId="0" shapeId="0">
       <text>
-        <t>", / (x4), 2px, &lt; (x8), &gt; (x8), div (x8), 
+        <t>", 2px, &gt;, 
 -- 82 ONLY --
- " (x7), = (x4), cell (x4), class (x4), dark (x4), visit, w3schools</t>
+ " (x7), / (x4), &lt; (x8), = (x4), &gt; (x7), cell (x4), class (x4), dark (x4), div (x8), visit, w3schools</t>
       </text>
     </comment>
     <comment ref="E23" authorId="0" shapeId="0">
@@ -3688,70 +3682,64 @@
       <text>
         <t>2px, 
 -- 4 ONLY --
- ", / (x11), &lt; (x22), &gt; (x23), div (x22)</t>
+ ", &gt;</t>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>", / (x11), &lt; (x14), &gt; (x14), div (x9), 
+        <t>", &gt;, 
 -- 4 ONLY --
- 2px, &lt; (x8), &gt; (x9), div (x13)</t>
+ 2px</t>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>/ (x2), &lt;, &gt;, 
+        <t>&gt;, 
 -- 4 ONLY --
- ", / (x9), 2px, &lt; (x21), &gt; (x22), div (x22)</t>
+ ", 2px</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>/, &lt;, &gt; (x2), 
+        <t>&gt;, 
 -- 4 ONLY --
- ", / (x10), 2px, &lt; (x21), &gt; (x21), div (x22)</t>
+ ", 2px</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>/ (x11), &lt; (x16), &gt; (x16), div (x16), 
+        <t>&gt;, 
 -- 4 ONLY --
- ", 2px, &lt; (x6), &gt; (x7), div (x6)</t>
+ ", 2px</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>2px, &lt;, 
+        <t>2px, 
 -- 4 ONLY --
- ", / (x11), &lt; (x21), &gt; (x23), div (x22)</t>
+ ", &gt;</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>", 2px, &lt;, &gt;, div (x2), 
--- 4 ONLY --
- / (x11), &lt; (x21), &gt; (x22), div (x20)</t>
+        <t>", 2px, &gt;</t>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>", /, 2px, &lt; (x2), &gt; (x2), div (x2), 
--- 4 ONLY --
- / (x10), &lt; (x20), &gt; (x21), div (x20)</t>
+        <t>", 2px, &gt;</t>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
         <t>", 
 -- 4 ONLY --
- / (x11), 2px, &lt; (x22), &gt; (x23), div (x22)</t>
+ 2px, &gt;</t>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>", / (x4), 2px, &lt; (x8), &gt; (x8), div (x8), 
--- 4 ONLY --
- / (x7), &lt; (x14), &gt; (x15), div (x14)</t>
+        <t>", 2px, &gt;</t>
       </text>
     </comment>
     <comment ref="D5" authorId="0" shapeId="0">
@@ -3833,9 +3821,9 @@
     </comment>
     <comment ref="D6" authorId="0" shapeId="0">
       <text>
-        <t>", / (x11), &lt; (x14), &gt; (x14), div (x9), 
+        <t>", &gt;, 
 -- 20 ONLY --
- ! (x2), " (x11), - (x3), . (x3), /, 50px (x2), : (x4), ; (x3), = (x6), Board, Chess, Visit, W3Schools, a (x2), background, black, body (x2), cell (x4), class (x4), color, com (x2), dark (x4), doctype, height, href, https, style, w3schools, width, www</t>
+ ! (x2), " (x11), - (x3), . (x3), / (x12), 50px (x2), : (x4), ; (x3), &lt; (x14), = (x6), &gt; (x13), Board, Chess, Visit, W3Schools, a (x2), background, black, body (x2), cell (x4), class (x4), color, com (x2), dark (x4), div (x9), doctype, height, href, https, style, w3schools, width, www</t>
       </text>
     </comment>
     <comment ref="E6" authorId="0" shapeId="0">
@@ -3968,140 +3956,140 @@
       <text>
         <t>., 
 -- 30 ONLY --
-  , * (x2), ,, / (x2), &lt;, &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+ * (x2), ,, / (x2), 50, &lt;, &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
       </text>
     </comment>
     <comment ref="D9" authorId="0" shapeId="0">
+      <text>
+        <t>&gt;, 
+-- 30 ONLY --
+ * (x2), ,, ., / (x2), 50, &lt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <t>., / (x2), &lt;, &gt;, a (x2), black, 
+-- 30 ONLY --
+ * (x2), ,, 50, I (x2), able (x2), about, allignmenot, along, and, basic, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="0" shapeId="0">
+      <text>
+        <t>chess, 
+-- 30 ONLY --
+ * (x2), ,, ., / (x2), 50, &lt;, &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="K9" authorId="0" shapeId="0">
+      <text>
+        <t>/, &lt;, &gt;, html, 
+-- 30 ONLY --
+ * (x2), ,, ., /, 50, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="N9" authorId="0" shapeId="0">
       <text>
         <t>/ (x2), &lt;, &gt;, 
 -- 30 ONLY --
-  , * (x2), ,, ., I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="F9" authorId="0" shapeId="0">
-      <text>
-        <t>., / (x2), &lt;, &gt;, a (x2), black, 
+ * (x2), ,, ., 50, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="O9" authorId="0" shapeId="0">
+      <text>
+        <t>., &lt;, black, 
 -- 30 ONLY --
-  , * (x2), ,, I (x2), able (x2), about, allignmenot, along, and, basic, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="H9" authorId="0" shapeId="0">
+ * (x2), ,, / (x2), 50, &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="Q9" authorId="0" shapeId="0">
+      <text>
+        <t>&lt;, &gt;, black, 
+-- 30 ONLY --
+ * (x2), ,, ., / (x2), 50, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="R9" authorId="0" shapeId="0">
       <text>
         <t>chess, 
 -- 30 ONLY --
-  , * (x2), ,, ., / (x2), &lt;, &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="K9" authorId="0" shapeId="0">
-      <text>
-        <t>/, &lt;, &gt;, html, 
+ * (x2), ,, ., / (x2), 50, &lt;, &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="S9" authorId="0" shapeId="0">
+      <text>
+        <t>/, &lt;, &gt;, black, chess, 
 -- 30 ONLY --
-  , * (x2), ,, ., /, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="N9" authorId="0" shapeId="0">
+ * (x2), ,, ., /, 50, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, bus, but, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+      </text>
+    </comment>
+    <comment ref="W9" authorId="0" shapeId="0">
       <text>
         <t>/ (x2), &lt;, &gt;, 
 -- 30 ONLY --
-  , * (x2), ,, ., I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="O9" authorId="0" shapeId="0">
-      <text>
-        <t>., &lt;, black, 
--- 30 ONLY --
-  , * (x2), ,, / (x2), &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="Q9" authorId="0" shapeId="0">
-      <text>
-        <t>&lt;, &gt;, black, 
--- 30 ONLY --
-  , * (x2), ,, ., / (x2), I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="R9" authorId="0" shapeId="0">
-      <text>
-        <t>chess, 
--- 30 ONLY --
-  , * (x2), ,, ., / (x2), &lt;, &gt;, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="S9" authorId="0" shapeId="0">
-      <text>
-        <t>/, &lt;, &gt;, black, chess, 
--- 30 ONLY --
-  , * (x2), ,, ., /, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, bus, but, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
-      </text>
-    </comment>
-    <comment ref="W9" authorId="0" shapeId="0">
-      <text>
-        <t>/ (x2), &lt;, &gt;, 
--- 30 ONLY --
-  , * (x2), ,, ., I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
+ * (x2), ,, ., 50, I (x2), a (x2), able (x2), about, allignmenot, along, and, basic, black, bus, but, chess, colors, constructed, follow, form, gain, get, hight, how, html, insight, into, is, late, marging, not, of, pixels, program, px, some, talking, the, title, to (x2), turned, up, was (x2), were, when, working, you</t>
       </text>
     </comment>
     <comment ref="D11" authorId="0" shapeId="0">
+      <text>
+        <t>&gt;, 
+-- 40 ONLY --
+ /, &lt;, &gt;, html</t>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="0" shapeId="0">
       <text>
         <t>/, &lt;, &gt; (x2), 
 -- 40 ONLY --
  html</t>
       </text>
     </comment>
-    <comment ref="F11" authorId="0" shapeId="0">
+    <comment ref="I11" authorId="0" shapeId="0">
+      <text>
+        <t>/, &lt;, &gt;, html, 
+-- 40 ONLY --
+ &gt;</t>
+      </text>
+    </comment>
+    <comment ref="N11" authorId="0" shapeId="0">
       <text>
         <t>/, &lt;, &gt; (x2), 
 -- 40 ONLY --
  html</t>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0">
-      <text>
-        <t>/, &lt;, &gt;, html, 
+    <comment ref="O11" authorId="0" shapeId="0">
+      <text>
+        <t>&lt;, 
 -- 40 ONLY --
- &gt;</t>
-      </text>
-    </comment>
-    <comment ref="N11" authorId="0" shapeId="0">
+ /, &gt; (x2), html</t>
+      </text>
+    </comment>
+    <comment ref="Q11" authorId="0" shapeId="0">
+      <text>
+        <t>&lt;, &gt;, 
+-- 40 ONLY --
+ /, &gt;, html</t>
+      </text>
+    </comment>
+    <comment ref="S11" authorId="0" shapeId="0">
       <text>
         <t>/, &lt;, &gt; (x2), 
 -- 40 ONLY --
  html</t>
       </text>
     </comment>
-    <comment ref="O11" authorId="0" shapeId="0">
-      <text>
-        <t>&lt;, 
--- 40 ONLY --
- /, &gt; (x2), html</t>
-      </text>
-    </comment>
-    <comment ref="Q11" authorId="0" shapeId="0">
-      <text>
-        <t>&lt;, &gt;, 
--- 40 ONLY --
- /, &gt;, html</t>
-      </text>
-    </comment>
-    <comment ref="S11" authorId="0" shapeId="0">
+    <comment ref="W11" authorId="0" shapeId="0">
       <text>
         <t>/, &lt;, &gt; (x2), 
 -- 40 ONLY --
  html</t>
       </text>
     </comment>
-    <comment ref="W11" authorId="0" shapeId="0">
-      <text>
-        <t>/, &lt;, &gt; (x2), 
--- 40 ONLY --
- html</t>
-      </text>
-    </comment>
     <comment ref="D14" authorId="0" shapeId="0">
       <text>
-        <t>/ (x11), &lt; (x16), &gt; (x16), div (x16), 
+        <t>&gt;, 
 -- 55 ONLY --
- /, 0px (x2), 440px, : (x2), ; (x2), green, margin, padding</t>
+ / (x12), 0px (x2), 440px, : (x2), ; (x2), &lt; (x16), &gt; (x15), div (x16), green, margin, padding</t>
       </text>
     </comment>
     <comment ref="E14" authorId="0" shapeId="0">
@@ -4183,9 +4171,9 @@
     </comment>
     <comment ref="D15" authorId="0" shapeId="0">
       <text>
-        <t>2px, &lt;, 
+        <t>2px, 
 -- 67 ONLY --
- -, ., 400px, : (x3), ; (x3), black, border (x2), class, collapse (x2), height, solid, table</t>
+ -, ., 400px, : (x3), ; (x3), &lt;, black, border (x2), class, collapse (x2), height, solid, table</t>
       </text>
     </comment>
     <comment ref="E15" authorId="0" shapeId="0">
@@ -4300,9 +4288,9 @@
     </comment>
     <comment ref="D17" authorId="0" shapeId="0">
       <text>
-        <t>", 2px, &lt;, &gt;, div (x2), 
+        <t>", 2px, &gt;, 
 -- 72 ONLY --
- !, (, ), - (x4), 10px (x2), 2px, 50px (x2), 5px (x2), : (x9), ; (x9), =, Inline, Not, background, black (x2), block, border, color, display, gray, height, inline, margin (x2), padding (x2), recommended, solid, style (x2), width, with</t>
+ !, (, ), - (x4), 10px (x2), 2px, 50px (x2), 5px (x2), : (x9), ; (x9), &lt;, =, Inline, Not, background, black (x2), block, border, color, display, div (x2), gray, height, inline, margin (x2), padding (x2), recommended, solid, style (x2), width, with</t>
       </text>
     </comment>
     <comment ref="E17" authorId="0" shapeId="0">
@@ -4475,9 +4463,9 @@
     </comment>
     <comment ref="D19" authorId="0" shapeId="0">
       <text>
-        <t>", /, 2px, &lt; (x2), &gt; (x2), div (x2), 
+        <t>", 2px, &gt;, 
 -- 77 ONLY --
- ", -, 50px (x2), : (x3), ; (x3), =, background, black, board, chess, color, height, style, visit, w3schools, width</t>
+ ", -, /, 50px (x2), : (x3), ; (x3), &lt; (x2), =, &gt;, background, black, board, chess, color, div (x2), height, style, visit, w3schools, width</t>
       </text>
     </comment>
     <comment ref="E19" authorId="0" shapeId="0">
@@ -4662,9 +4650,9 @@
     </comment>
     <comment ref="D23" authorId="0" shapeId="0">
       <text>
-        <t>", / (x4), 2px, &lt; (x8), &gt; (x8), div (x8), 
+        <t>", 2px, &gt;, 
 -- 82 ONLY --
- " (x7), = (x4), cell (x4), class (x4), dark (x4), visit, w3schools</t>
+ " (x7), / (x4), &lt; (x8), = (x4), &gt; (x7), cell (x4), class (x4), dark (x4), div (x8), visit, w3schools</t>
       </text>
     </comment>
     <comment ref="E23" authorId="0" shapeId="0">
@@ -10738,32 +10726,32 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="3" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R4" s="4" t="n"/>
       <c r="S4" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T4" s="4" t="n"/>
       <c r="U4" s="4" t="n"/>
@@ -10771,7 +10759,7 @@
         <v>1</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -10841,7 +10829,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4</v>
@@ -10977,7 +10965,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="3" t="n">
@@ -11061,7 +11049,7 @@
       </c>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="3" t="n">
@@ -11173,7 +11161,7 @@
       </c>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="3" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>6</v>
@@ -11229,7 +11217,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>6</v>
@@ -11327,7 +11315,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>10</v>
@@ -11441,7 +11429,7 @@
       </c>
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>6</v>
@@ -11623,7 +11611,7 @@
       </c>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="3" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>1</v>
@@ -14534,32 +14522,32 @@
         <v>2.1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>4</v>
       </c>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="3" t="n">
-        <v>7.7</v>
+        <v>1.9</v>
       </c>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="3" t="n">
-        <v>7.6</v>
+        <v>1.9</v>
       </c>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
-      <c r="N4" s="5" t="n">
-        <v>115.4</v>
+      <c r="N4" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="3" t="n">
-        <v>12.3</v>
+        <v>6.2</v>
       </c>
       <c r="R4" s="4" t="n"/>
       <c r="S4" s="3" t="n">
-        <v>18</v>
+        <v>6.2</v>
       </c>
       <c r="T4" s="4" t="n"/>
       <c r="U4" s="4" t="n"/>
@@ -14567,7 +14555,7 @@
         <v>2.1</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>59</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="5">
@@ -14637,7 +14625,7 @@
         <v>2.5</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>4</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>7.6</v>
@@ -14645,31 +14633,31 @@
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="3" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
       <c r="N6" s="5" t="n">
-        <v>102.6</v>
+        <v>107</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>5.2</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>56.7</v>
+        <v>57.1</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>57.1</v>
+        <v>57.8</v>
       </c>
       <c r="T6" s="4" t="n"/>
       <c r="U6" s="4" t="n"/>
@@ -14677,7 +14665,7 @@
         <v>15.3</v>
       </c>
       <c r="W6" s="5" t="n">
-        <v>118.3</v>
+        <v>120.9</v>
       </c>
     </row>
     <row r="7">
@@ -14773,11 +14761,11 @@
         <v>2.5</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>7.7</v>
+        <v>1.9</v>
       </c>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="3" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="3" t="n">
@@ -14785,31 +14773,31 @@
       </c>
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
       <c r="N9" s="3" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="P9" s="4" t="n"/>
       <c r="Q9" s="3" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
       <c r="V9" s="4" t="n"/>
       <c r="W9" s="3" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="10">
@@ -14857,39 +14845,39 @@
       </c>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="3" t="n">
-        <v>7.6</v>
+        <v>1.9</v>
       </c>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
       <c r="M11" s="4" t="n"/>
       <c r="N11" s="3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="R11" s="4" t="n"/>
       <c r="S11" s="3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="T11" s="4" t="n"/>
       <c r="U11" s="4" t="n"/>
       <c r="V11" s="4" t="n"/>
       <c r="W11" s="3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="12">
@@ -14968,38 +14956,38 @@
         </is>
       </c>
       <c r="C14" s="4" t="n"/>
-      <c r="D14" s="5" t="n">
-        <v>115.4</v>
+      <c r="D14" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>102.6</v>
+        <v>107</v>
       </c>
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="n"/>
       <c r="I14" s="3" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
       <c r="O14" s="3" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
       <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n"/>
@@ -15007,7 +14995,7 @@
         <v>3.8</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>54.7</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="15">
@@ -15025,37 +15013,37 @@
         <v>2.5</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="3" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
       <c r="N15" s="3" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>7.6</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="T15" s="4" t="n"/>
       <c r="U15" s="3" t="n">
@@ -15065,7 +15053,7 @@
         <v>6.5</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="16">
@@ -15123,39 +15111,39 @@
         <v>2.5</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>12.3</v>
+        <v>6.2</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>56.7</v>
+        <v>57.1</v>
       </c>
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="3" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="P17" s="4" t="n"/>
       <c r="R17" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="T17" s="4" t="n"/>
       <c r="U17" s="4" t="n"/>
@@ -15163,7 +15151,7 @@
         <v>13.2</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -15237,38 +15225,38 @@
       </c>
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="3" t="n">
-        <v>18</v>
+        <v>6.2</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>57.1</v>
+        <v>57.8</v>
       </c>
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="3" t="n">
         <v>5</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L19" s="4" t="n"/>
       <c r="M19" s="4" t="n"/>
       <c r="N19" s="3" t="n">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>15.2</v>
@@ -15279,7 +15267,7 @@
         <v>15.3</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>27.6</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="20">
@@ -15419,42 +15407,42 @@
       </c>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="3" t="n">
-        <v>59</v>
+        <v>6.2</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>118.3</v>
+        <v>120.9</v>
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="3" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L23" s="4" t="n"/>
       <c r="M23" s="4" t="n"/>
       <c r="N23" s="3" t="n">
-        <v>54.7</v>
+        <v>57.3</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>27.6</v>
+        <v>28.2</v>
       </c>
       <c r="T23" s="4" t="n"/>
       <c r="U23" s="4" t="n"/>
